--- a/data/trans_camb/DC-Edad-trans_camb.xlsx
+++ b/data/trans_camb/DC-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,38</t>
+          <t>-3,0; 2,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; -0,71</t>
+          <t>-5,06; -0,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 9,78</t>
+          <t>-0,84; 9,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,17; -0,26</t>
+          <t>-10,57; -0,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,89; -6,66</t>
+          <t>-16,1; -6,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 11,22</t>
+          <t>-3,69; 10,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,01</t>
+          <t>-5,64; 0,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,48; -4,34</t>
+          <t>-9,45; -4,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 7,1</t>
+          <t>-1,47; 7,65</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,83; 80,62</t>
+          <t>-53,68; 70,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-88,91; -17,48</t>
+          <t>-88,75; -11,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 286,75</t>
+          <t>-20,79; 277,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,56; -0,12</t>
+          <t>-44,92; -2,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,72; -35,51</t>
+          <t>-67,46; -35,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 57,87</t>
+          <t>-15,88; 54,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,55; 0,33</t>
+          <t>-42,06; 1,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,15; -38,44</t>
+          <t>-68,13; -38,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 64,2</t>
+          <t>-11,38; 67,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -0,02</t>
+          <t>-5,8; -0,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,66; -2,14</t>
+          <t>-7,46; -2,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 5,87</t>
+          <t>-2,49; 5,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,43; -5,62</t>
+          <t>-14,37; -5,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -6,52</t>
+          <t>-15,89; -6,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 34,65</t>
+          <t>0,59; 40,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,02; -3,78</t>
+          <t>-8,84; -3,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -5,21</t>
+          <t>-10,34; -4,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 27,04</t>
+          <t>1,31; 27,03</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 0,26</t>
+          <t>-56,14; -4,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,54; -30,27</t>
+          <t>-76,26; -29,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 80,74</t>
+          <t>-26,93; 73,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,44; -25,73</t>
+          <t>-53,86; -25,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,89; -28,81</t>
+          <t>-57,68; -29,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 150,23</t>
+          <t>2,51; 181,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,05; -25,5</t>
+          <t>-51,0; -25,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,72; -34,68</t>
+          <t>-58,72; -31,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 180,73</t>
+          <t>6,43; 171,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,68; -4,51</t>
+          <t>-11,55; -4,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,89; -4,96</t>
+          <t>-11,9; -5,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 3,26</t>
+          <t>-4,81; 3,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 2,12</t>
+          <t>-6,95; 2,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,39; -6,25</t>
+          <t>-14,68; -6,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 10,7</t>
+          <t>-2,36; 10,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,04; -2,24</t>
+          <t>-8,13; -2,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,26; -7,0</t>
+          <t>-12,42; -6,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,54</t>
+          <t>-1,47; 5,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,44; -32,83</t>
+          <t>-65,59; -33,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-68,48; -36,21</t>
+          <t>-67,49; -37,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 23,35</t>
+          <t>-28,93; 24,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 10,1</t>
+          <t>-27,18; 12,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,56; -30,45</t>
+          <t>-59,03; -29,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 53,73</t>
+          <t>-7,46; 51,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,66; -12,91</t>
+          <t>-38,88; -12,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,43; -39,48</t>
+          <t>-59,46; -38,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 30,48</t>
+          <t>-6,19; 31,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,02; -7,28</t>
+          <t>-15,49; -6,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,75; -7,24</t>
+          <t>-15,5; -6,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 4,63</t>
+          <t>-16,02; 4,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -2,04</t>
+          <t>-12,4; -1,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,78; -5,93</t>
+          <t>-15,83; -5,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,55</t>
+          <t>1,65; 12,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,37; -5,54</t>
+          <t>-12,28; -5,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,34; -7,71</t>
+          <t>-14,42; -7,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 7,27</t>
+          <t>-9,5; 7,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,71; -38,8</t>
+          <t>-65,97; -36,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,5; -38,29</t>
+          <t>-65,19; -35,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,48; 23,04</t>
+          <t>-65,72; 20,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,92; -7,85</t>
+          <t>-40,74; -6,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,51; -23,46</t>
+          <t>-51,06; -21,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,01; 54,74</t>
+          <t>5,61; 52,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,06; -24,54</t>
+          <t>-47,4; -23,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,12; -34,56</t>
+          <t>-55,11; -34,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 31,13</t>
+          <t>-36,69; 30,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,25; -12,92</t>
+          <t>-24,85; -12,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,26; -10,63</t>
+          <t>-22,63; -11,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 3,45</t>
+          <t>-8,3; 3,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 4,39</t>
+          <t>-8,26; 4,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 0,22</t>
+          <t>-11,56; -0,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,51; 18,74</t>
+          <t>7,93; 18,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,3; -5,5</t>
+          <t>-14,07; -5,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -6,7</t>
+          <t>-15,28; -7,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 9,5</t>
+          <t>1,21; 9,54</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,36; -43,92</t>
+          <t>-69,01; -44,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,8; -37,22</t>
+          <t>-63,67; -37,78</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 11,88</t>
+          <t>-23,74; 12,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 16,16</t>
+          <t>-23,97; 17,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 1,68</t>
+          <t>-34,35; -0,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,78; 70,71</t>
+          <t>22,47; 69,4</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,95; -19,4</t>
+          <t>-41,58; -19,59</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,76; -23,46</t>
+          <t>-45,84; -23,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4,3; 33,35</t>
+          <t>3,55; 33,38</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 0,22</t>
+          <t>-14,22; 0,34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,61; -5,29</t>
+          <t>-17,98; -5,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 8,69</t>
+          <t>-3,03; 8,57</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 0,54</t>
+          <t>-14,13; -0,21</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,26; -10,54</t>
+          <t>-23,63; -10,6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,53; 48,25</t>
+          <t>4,69; 44,72</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,74; -1,81</t>
+          <t>-11,48; -1,29</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-19,45; -9,99</t>
+          <t>-19,05; -9,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,07; 39,77</t>
+          <t>2,97; 40,3</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-43,12; 1,42</t>
+          <t>-45,5; 1,31</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-58,94; -21,0</t>
+          <t>-58,79; -22,83</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 38,23</t>
+          <t>-9,92; 37,78</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 1,49</t>
+          <t>-30,63; -0,21</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-52,44; -28,04</t>
+          <t>-53,2; -27,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,39; 136,22</t>
+          <t>11,44; 124,48</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,71; -5,7</t>
+          <t>-31,4; -4,31</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-52,38; -30,38</t>
+          <t>-51,92; -30,74</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8,5; 120,67</t>
+          <t>8,15; 116,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-19,71; -2,35</t>
+          <t>-19,52; -2,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-22,01; -6,6</t>
+          <t>-21,6; -5,98</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 13,13</t>
+          <t>-3,82; 12,29</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 13,48</t>
+          <t>-2,26; 13,03</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 2,19</t>
+          <t>-12,24; 2,8</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,48; 28,49</t>
+          <t>15,47; 28,57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 4,94</t>
+          <t>-6,27; 4,92</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,87; -2,47</t>
+          <t>-14,27; -2,76</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,96; 19,77</t>
+          <t>9,91; 19,85</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-47,34; -7,45</t>
+          <t>-47,34; -7,25</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-52,71; -20,0</t>
+          <t>-52,66; -19,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 41,65</t>
+          <t>-8,6; 39,73</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 41,12</t>
+          <t>-5,57; 39,12</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-29,59; 6,59</t>
+          <t>-30,16; 9,45</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,43; 88,53</t>
+          <t>36,48; 88,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 14,97</t>
+          <t>-15,87; 14,38</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,9; -7,08</t>
+          <t>-35,93; -8,08</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>24,31; 58,33</t>
+          <t>23,92; 58,54</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -5,44</t>
+          <t>-8,89; -5,59</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,59; -6,4</t>
+          <t>-9,89; -6,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,08</t>
+          <t>-1,78; 5,15</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,16; -2,0</t>
+          <t>-6,31; -1,93</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -7,47</t>
+          <t>-11,43; -7,31</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,71; 25,4</t>
+          <t>9,9; 25,26</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -4,23</t>
+          <t>-6,87; -4,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -7,44</t>
+          <t>-9,94; -7,31</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,53; 16,15</t>
+          <t>5,57; 15,07</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-47,45; -32,95</t>
+          <t>-47,94; -33,64</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-52,57; -37,94</t>
+          <t>-53,01; -38,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 30,35</t>
+          <t>-9,21; 30,8</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-21,15; -7,26</t>
+          <t>-21,42; -7,26</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-40,24; -28,01</t>
+          <t>-39,49; -27,42</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,71; 93,93</t>
+          <t>35,05; 92,26</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-29,6; -19,24</t>
+          <t>-29,2; -18,1</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-42,51; -33,46</t>
+          <t>-42,64; -33,14</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>23,99; 70,52</t>
+          <t>23,81; 65,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/DC-Edad-trans_camb.xlsx
+++ b/data/trans_camb/DC-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>3,51</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,13</t>
+          <t>-2,91; 2,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; -0,58</t>
+          <t>-5,1; -0,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 9,68</t>
+          <t>-0,24; 9,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,57; -0,51</t>
+          <t>-10,43; -0,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,1; -6,97</t>
+          <t>-15,89; -6,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 10,26</t>
+          <t>-3,63; 11,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 0,26</t>
+          <t>-5,59; 0,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,45; -4,36</t>
+          <t>-9,47; -4,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 7,65</t>
+          <t>-0,5; 8,28</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,68; 70,48</t>
+          <t>-54,19; 72,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-88,75; -11,96</t>
+          <t>-87,77; -18,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 277,3</t>
+          <t>-11,53; 292,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,92; -2,26</t>
+          <t>-44,41; -0,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,46; -35,42</t>
+          <t>-66,96; -35,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 54,29</t>
+          <t>-16,44; 62,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 1,73</t>
+          <t>-41,02; 1,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,13; -38,24</t>
+          <t>-68,17; -37,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 67,26</t>
+          <t>-4,16; 72,63</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,84</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>1,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -0,38</t>
+          <t>-5,49; -0,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; -2,25</t>
+          <t>-7,75; -2,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 5,46</t>
+          <t>-2,26; 5,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -5,6</t>
+          <t>-14,46; -5,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,89; -6,79</t>
+          <t>-15,07; -6,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 40,49</t>
+          <t>-5,01; 6,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; -3,49</t>
+          <t>-8,92; -3,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -4,76</t>
+          <t>-10,16; -4,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 27,03</t>
+          <t>-1,64; 5,28</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,14; -4,27</t>
+          <t>-54,96; -3,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-76,26; -29,62</t>
+          <t>-76,08; -30,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 73,45</t>
+          <t>-24,07; 73,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,86; -25,29</t>
+          <t>-54,61; -24,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,68; -29,98</t>
+          <t>-56,14; -29,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 181,05</t>
+          <t>-18,25; 27,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,0; -25,06</t>
+          <t>-49,66; -24,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,72; -31,6</t>
+          <t>-58,13; -32,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 171,5</t>
+          <t>-10,18; 35,68</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>8,35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>3,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,55; -4,51</t>
+          <t>-11,6; -4,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,9; -5,38</t>
+          <t>-12,09; -4,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 3,4</t>
+          <t>-5,76; 2,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 2,5</t>
+          <t>-6,72; 2,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,68; -6,23</t>
+          <t>-14,58; -5,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 10,68</t>
+          <t>3,74; 12,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,13; -2,23</t>
+          <t>-8,06; -2,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,42; -6,68</t>
+          <t>-12,39; -6,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 5,53</t>
+          <t>0,26; 6,28</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-6,48%</t>
+          <t>-11,2%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,59; -33,19</t>
+          <t>-66,58; -32,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,49; -37,14</t>
+          <t>-68,36; -36,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 24,64</t>
+          <t>-32,52; 16,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 12,6</t>
+          <t>-27,04; 11,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,03; -29,72</t>
+          <t>-58,4; -29,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 51,61</t>
+          <t>14,78; 63,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,88; -12,48</t>
+          <t>-38,44; -12,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,46; -38,22</t>
+          <t>-59,48; -38,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 31,48</t>
+          <t>1,26; 35,85</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,76</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,91</t>
+          <t>9,9</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>6,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -6,73</t>
+          <t>-15,37; -6,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,5; -6,59</t>
+          <t>-15,27; -6,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 4,24</t>
+          <t>-2,71; 7,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,4; -1,72</t>
+          <t>-11,88; -1,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,83; -5,41</t>
+          <t>-15,38; -5,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 12,96</t>
+          <t>4,78; 14,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,28; -5,3</t>
+          <t>-12,25; -5,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -7,63</t>
+          <t>-14,37; -7,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 7,1</t>
+          <t>2,82; 9,74</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-17,87%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,97; -36,33</t>
+          <t>-65,66; -38,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,19; -35,52</t>
+          <t>-65,16; -37,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,72; 20,72</t>
+          <t>-11,89; 40,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,74; -6,52</t>
+          <t>-39,67; -6,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,06; -21,88</t>
+          <t>-50,25; -22,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,61; 52,8</t>
+          <t>15,61; 57,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,4; -23,09</t>
+          <t>-46,98; -24,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-55,11; -34,3</t>
+          <t>-54,18; -34,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,69; 30,1</t>
+          <t>10,08; 43,01</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,14</t>
+          <t>-2,97</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,25</t>
+          <t>13,47</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,85; -12,78</t>
+          <t>-24,71; -13,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,63; -11,17</t>
+          <t>-23,23; -11,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 3,62</t>
+          <t>-9,02; 2,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 4,92</t>
+          <t>-8,46; 4,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,56; -0,12</t>
+          <t>-12,16; 0,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,93; 18,74</t>
+          <t>7,98; 19,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,07; -5,76</t>
+          <t>-14,27; -5,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,28; -7,09</t>
+          <t>-15,74; -7,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 9,54</t>
+          <t>0,93; 9,05</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-6,7%</t>
+          <t>-9,31%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,01; -44,35</t>
+          <t>-69,35; -44,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,67; -37,78</t>
+          <t>-64,85; -37,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 12,5</t>
+          <t>-25,38; 8,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 17,08</t>
+          <t>-25,54; 16,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-34,35; -0,15</t>
+          <t>-35,48; 0,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,47; 69,4</t>
+          <t>22,9; 71,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-41,58; -19,59</t>
+          <t>-41,94; -19,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,84; -23,99</t>
+          <t>-46,14; -24,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,55; 33,38</t>
+          <t>2,65; 31,9</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,07</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17,09</t>
+          <t>4,81</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 0,34</t>
+          <t>-13,42; -0,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-17,98; -5,45</t>
+          <t>-18,58; -5,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 8,57</t>
+          <t>-4,34; 8,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -0,21</t>
+          <t>-14,1; -0,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,63; -10,6</t>
+          <t>-23,6; -10,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,69; 44,72</t>
+          <t>1,49; 13,98</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,48; -1,29</t>
+          <t>-11,63; -1,86</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-19,05; -9,92</t>
+          <t>-19,3; -10,34</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,97; 40,3</t>
+          <t>0,7; 9,67</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-45,5; 1,31</t>
+          <t>-42,87; 0,04</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-58,79; -22,83</t>
+          <t>-59,33; -21,61</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 37,78</t>
+          <t>-14,48; 36,45</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,63; -0,21</t>
+          <t>-31,03; -0,56</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-53,2; -27,79</t>
+          <t>-52,67; -27,83</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,44; 124,48</t>
+          <t>2,91; 37,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,4; -4,31</t>
+          <t>-30,89; -5,66</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-51,92; -30,74</t>
+          <t>-51,7; -31,1</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8,15; 116,55</t>
+          <t>1,61; 30,37</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,85</t>
+          <t>22,48</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15,04</t>
+          <t>15,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-19,52; -2,45</t>
+          <t>-20,33; -3,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-21,6; -5,98</t>
+          <t>-22,48; -5,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 12,29</t>
+          <t>-2,76; 13,06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 13,03</t>
+          <t>-2,98; 12,78</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 2,8</t>
+          <t>-13,17; 2,8</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,47; 28,57</t>
+          <t>16,12; 28,84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 4,92</t>
+          <t>-6,92; 4,8</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -2,76</t>
+          <t>-14,15; -2,83</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,91; 19,85</t>
+          <t>10,14; 20,42</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-47,34; -7,25</t>
+          <t>-48,69; -8,65</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-52,66; -19,03</t>
+          <t>-54,3; -18,35</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 39,73</t>
+          <t>-6,47; 42,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 39,12</t>
+          <t>-7,07; 39,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 9,45</t>
+          <t>-31,57; 8,2</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,48; 88,41</t>
+          <t>38,54; 88,56</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 14,38</t>
+          <t>-17,68; 14,24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-35,93; -8,08</t>
+          <t>-35,31; -8,63</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>23,92; 58,54</t>
+          <t>25,02; 61,73</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,49</t>
+          <t>10,91</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>7,58</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -5,59</t>
+          <t>-8,94; -5,53</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -6,41</t>
+          <t>-9,69; -6,46</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 5,15</t>
+          <t>1,93; 5,77</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -1,93</t>
+          <t>-6,32; -1,96</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-11,43; -7,31</t>
+          <t>-11,56; -7,43</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,9; 25,26</t>
+          <t>9,05; 13,09</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-6,87; -4,06</t>
+          <t>-6,96; -4,2</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -7,31</t>
+          <t>-9,97; -7,41</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,57; 15,07</t>
+          <t>6,15; 9,08</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-47,94; -33,64</t>
+          <t>-48,6; -33,0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-53,01; -38,23</t>
+          <t>-52,57; -38,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 30,8</t>
+          <t>10,59; 34,77</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-21,42; -7,26</t>
+          <t>-21,6; -7,21</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-39,49; -27,42</t>
+          <t>-39,64; -27,54</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,05; 92,26</t>
+          <t>31,36; 48,94</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-29,2; -18,1</t>
+          <t>-29,47; -18,92</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-42,64; -33,14</t>
+          <t>-42,53; -33,43</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>23,81; 65,41</t>
+          <t>26,1; 41,19</t>
         </is>
       </c>
     </row>
